--- a/2_Formulas_Functions/8_Text_Functions.xlsx
+++ b/2_Formulas_Functions/8_Text_Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Developer\_Courses\Excel\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xdrtas\sources\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289F5FEB-D4A0-4E30-9E0C-8AA9F558B1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550ACA86-DF77-4013-9631-6A7F8A34415E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11993" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -566,7 +566,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -658,52 +658,52 @@
               <c:strCache>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>Kafka</c:v>
+                  <c:v>Tableau</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>DataBricks</c:v>
+                  <c:v>SQL</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Spark</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>Snowflake</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Scala</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>R</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Python</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>Power BI</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Kafka</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Java</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Hadoop</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>GCP</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>Power BI</c:v>
+                <c:pt idx="12">
+                  <c:v>Excel</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>Airflow</c:v>
+                <c:pt idx="13">
+                  <c:v>DataBricks</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>Hadoop</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>R</c:v>
-                </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="14">
                   <c:v>Azure</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>Java</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>SQL</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Snowflake</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Scala</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Excel</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>Tableau</c:v>
+                  <c:v>Airflow</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -715,34 +715,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>6</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>7</c:v>
@@ -751,16 +751,16 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1785,27 +1785,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B5E7F13-C613-4452-9CDB-2C26D6876D9D}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" customWidth="1"/>
-    <col min="2" max="2" width="14.265625" customWidth="1"/>
-    <col min="3" max="3" width="27.265625" customWidth="1"/>
-    <col min="4" max="4" width="17.59765625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="26.265625" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="8.86328125" customWidth="1"/>
-    <col min="10" max="10" width="34.73046875" customWidth="1"/>
-    <col min="11" max="11" width="8.86328125" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="13" max="13" width="15.46484375" customWidth="1"/>
-    <col min="14" max="14" width="8.86328125" customWidth="1"/>
-    <col min="15" max="15" width="16.3984375" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="9" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="11" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" customWidth="1"/>
+    <col min="10" max="10" width="34.7109375" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="19" width="0" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -1853,7 +1856,7 @@
       <c r="U1" s="17"/>
       <c r="V1" s="17"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
@@ -1877,6 +1880,21 @@
       </c>
       <c r="H2" s="6" t="s">
         <v>11</v>
+      </c>
+      <c r="J2" t="str">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,F2:G2)</f>
+        <v>457 Oak St San Jose, CA, 95101</v>
+      </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:M2">_xlfn.TEXTSPLIT(B2, " ",)</f>
+        <v>Pam</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Beesly</v>
+      </c>
+      <c r="O2" t="str">
+        <f>RIGHT(A2,3)</f>
+        <v>548</v>
       </c>
       <c r="Q2">
         <f>FIND(",", G2)+LEN(", ")</f>
@@ -1890,8 +1908,20 @@
         <f>MID(G2,Q2,R2-Q2)</f>
         <v>CA</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T2">
+        <f>FIND(",",G2)+LEN(", ")</f>
+        <v>11</v>
+      </c>
+      <c r="U2">
+        <f>FIND(",",G2,T2)</f>
+        <v>13</v>
+      </c>
+      <c r="V2" t="str">
+        <f>MID(G2,T2,U2-T2)</f>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>71</v>
       </c>
@@ -1916,20 +1946,47 @@
       <c r="H3" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J21" si="0">_xlfn.TEXTJOIN(" ",TRUE,F3:G3)</f>
+        <v>203 Birch St Chicago, IL, 60601</v>
+      </c>
+      <c r="L3" t="str" cm="1">
+        <f t="array" ref="L3:M3">_xlfn.TEXTSPLIT(B3, " ",)</f>
+        <v>Michael</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Scott</v>
+      </c>
+      <c r="O3" t="str">
+        <f t="shared" ref="O3:O21" si="1">RIGHT(A3,3)</f>
+        <v>549</v>
+      </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q21" si="0">FIND(",", G3)+LEN(", ")</f>
+        <f t="shared" ref="Q3:Q21" si="2">FIND(",", G3)+LEN(", ")</f>
         <v>10</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R21" si="1">FIND(",",G3,Q3)</f>
+        <f t="shared" ref="R3:R21" si="3">FIND(",",G3,Q3)</f>
         <v>12</v>
       </c>
       <c r="S3" t="str">
-        <f t="shared" ref="S3:S21" si="2">MID(G3,Q3,R3-Q3)</f>
+        <f t="shared" ref="S3:S21" si="4">MID(G3,Q3,R3-Q3)</f>
         <v>IL</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T3">
+        <f t="shared" ref="T3:T21" si="5">FIND(",",G3)+LEN(", ")</f>
+        <v>10</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U21" si="6">FIND(",",G3,T3)</f>
+        <v>12</v>
+      </c>
+      <c r="V3" t="str">
+        <f t="shared" ref="V3:V21" si="7">MID(G3,T3,U3-T3)</f>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -1954,20 +2011,47 @@
       <c r="H4" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>790 Pine St Chicago, IL, 60601</v>
+      </c>
+      <c r="L4" t="str" cm="1">
+        <f t="array" ref="L4:M4">_xlfn.TEXTSPLIT(B4, " ",)</f>
+        <v>Kevin</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Malone</v>
+      </c>
+      <c r="O4" t="str">
+        <f t="shared" si="1"/>
+        <v>550</v>
+      </c>
       <c r="Q4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T4">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V4" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -1992,20 +2076,47 @@
       <c r="H5" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>457 Oak St San Jose, CA, 95101</v>
+      </c>
+      <c r="L5" t="str" cm="1">
+        <f t="array" ref="L5:M5">_xlfn.TEXTSPLIT(B5, " ",)</f>
+        <v>Pam</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Beesly</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" si="1"/>
+        <v>551</v>
+      </c>
       <c r="Q5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="R5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>CA</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T5">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="V5" t="str">
+        <f t="shared" si="7"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -2030,20 +2141,47 @@
       <c r="H6" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>459 Oak St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L6" t="str" cm="1">
+        <f t="array" ref="L6:M6">_xlfn.TEXTSPLIT(B6, " ",)</f>
+        <v>Jim</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="O6" t="str">
+        <f t="shared" si="1"/>
+        <v>552</v>
+      </c>
       <c r="Q6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T6">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V6" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -2068,20 +2206,47 @@
       <c r="H7" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>204 Birch St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L7" t="str" cm="1">
+        <f t="array" ref="L7:M7">_xlfn.TEXTSPLIT(B7, " ",)</f>
+        <v>Ryan</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Howard</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" si="1"/>
+        <v>553</v>
+      </c>
       <c r="Q7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T7">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V7" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -2106,20 +2271,47 @@
       <c r="H8" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>790 Pine St Chicago, IL, 60601</v>
+      </c>
+      <c r="L8" t="str" cm="1">
+        <f t="array" ref="L8:M8">_xlfn.TEXTSPLIT(B8, " ",)</f>
+        <v>Kevin</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Malone</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="1"/>
+        <v>554</v>
+      </c>
       <c r="Q8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T8">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V8" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
@@ -2144,20 +2336,47 @@
       <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>204 Birch St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L9" t="str" cm="1">
+        <f t="array" ref="L9:M9">_xlfn.TEXTSPLIT(B9, " ",)</f>
+        <v>Ryan</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Howard</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="1"/>
+        <v>555</v>
+      </c>
       <c r="Q9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T9">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V9" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -2182,20 +2401,47 @@
       <c r="H10" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>123 Elm St Chicago, IL, 60601</v>
+      </c>
+      <c r="L10" t="str" cm="1">
+        <f t="array" ref="L10:M10">_xlfn.TEXTSPLIT(B10, " ",)</f>
+        <v>Stanley</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Hudson</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="1"/>
+        <v>556</v>
+      </c>
       <c r="Q10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T10">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V10" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>80</v>
       </c>
@@ -2220,20 +2466,47 @@
       <c r="H11" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="J11" t="str">
+        <f t="shared" si="0"/>
+        <v>123 Elm St Los Angeles, CA, 90001</v>
+      </c>
+      <c r="L11" t="str" cm="1">
+        <f t="array" ref="L11:M11">_xlfn.TEXTSPLIT(B11, " ",)</f>
+        <v>Angela</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Martin</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="1"/>
+        <v>557</v>
+      </c>
       <c r="Q11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="R11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="S11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>CA</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T11">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="V11" t="str">
+        <f t="shared" si="7"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -2258,20 +2531,47 @@
       <c r="H12" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="J12" t="str">
+        <f t="shared" si="0"/>
+        <v>123 Elm St San Diego, CA, 92101</v>
+      </c>
+      <c r="L12" t="str" cm="1">
+        <f t="array" ref="L12:M12">_xlfn.TEXTSPLIT(B12, " ",)</f>
+        <v>Dwight</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Schrute</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" si="1"/>
+        <v>558</v>
+      </c>
       <c r="Q12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="R12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>CA</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T12">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="V12" t="str">
+        <f t="shared" si="7"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>82</v>
       </c>
@@ -2296,20 +2596,47 @@
       <c r="H13" s="6" t="s">
         <v>16</v>
       </c>
+      <c r="J13" t="str">
+        <f t="shared" si="0"/>
+        <v>202 Birch St Chicago, IL, 60601</v>
+      </c>
+      <c r="L13" t="str" cm="1">
+        <f t="array" ref="L13:M13">_xlfn.TEXTSPLIT(B13, " ",)</f>
+        <v>Oscar</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Martinez</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="1"/>
+        <v>559</v>
+      </c>
       <c r="Q13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T13">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V13" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
@@ -2334,20 +2661,47 @@
       <c r="H14" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="J14" t="str">
+        <f t="shared" si="0"/>
+        <v>204 Birch St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L14" t="str" cm="1">
+        <f t="array" ref="L14:M14">_xlfn.TEXTSPLIT(B14, " ",)</f>
+        <v>Ryan</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Howard</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="1"/>
+        <v>560</v>
+      </c>
       <c r="Q14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T14">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V14" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -2372,20 +2726,47 @@
       <c r="H15" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="J15" t="str">
+        <f t="shared" si="0"/>
+        <v>123 Elm St Chicago, IL, 60601</v>
+      </c>
+      <c r="L15" t="str" cm="1">
+        <f t="array" ref="L15:M15">_xlfn.TEXTSPLIT(B15, " ",)</f>
+        <v>Phyllis</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Vance</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="1"/>
+        <v>561</v>
+      </c>
       <c r="Q15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T15">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V15" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
@@ -2410,20 +2791,47 @@
       <c r="H16" s="6" t="s">
         <v>20</v>
       </c>
+      <c r="J16" t="str">
+        <f t="shared" si="0"/>
+        <v>456 Oak St Chicago, IL, 60601</v>
+      </c>
+      <c r="L16" t="str" cm="1">
+        <f t="array" ref="L16:M16">_xlfn.TEXTSPLIT(B16, " ",)</f>
+        <v>Meredith</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Palmer</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="1"/>
+        <v>562</v>
+      </c>
       <c r="Q16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T16">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V16" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -2448,20 +2856,47 @@
       <c r="H17" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="J17" t="str">
+        <f t="shared" si="0"/>
+        <v>203 Birch St Chicago, IL, 60602</v>
+      </c>
+      <c r="L17" t="str" cm="1">
+        <f t="array" ref="L17:M17">_xlfn.TEXTSPLIT(B17, " ",)</f>
+        <v>Michael</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Scott</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="1"/>
+        <v>563</v>
+      </c>
       <c r="Q17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T17">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V17" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -2486,20 +2921,47 @@
       <c r="H18" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="J18" t="str">
+        <f t="shared" si="0"/>
+        <v>459 Oak St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L18" t="str" cm="1">
+        <f t="array" ref="L18:M18">_xlfn.TEXTSPLIT(B18, " ",)</f>
+        <v>Jim</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="1"/>
+        <v>564</v>
+      </c>
       <c r="Q18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T18">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V18" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -2524,20 +2986,47 @@
       <c r="H19" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="J19" t="str">
+        <f t="shared" si="0"/>
+        <v>456 Oak St New York, NY, 10001</v>
+      </c>
+      <c r="L19" t="str" cm="1">
+        <f t="array" ref="L19:M19">_xlfn.TEXTSPLIT(B19, " ",)</f>
+        <v>Kelly</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Kapoor</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="1"/>
+        <v>565</v>
+      </c>
       <c r="Q19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="R19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>NY</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T19">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="V19" t="str">
+        <f t="shared" si="7"/>
+        <v>NY</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -2562,20 +3051,47 @@
       <c r="H20" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="J20" t="str">
+        <f t="shared" si="0"/>
+        <v>459 Oak St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L20" t="str" cm="1">
+        <f t="array" ref="L20:M20">_xlfn.TEXTSPLIT(B20, " ",)</f>
+        <v>Jim</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="1"/>
+        <v>566</v>
+      </c>
       <c r="Q20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="T20">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V20" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -2600,16 +3116,43 @@
       <c r="H21" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="J21" t="str">
+        <f t="shared" si="0"/>
+        <v>459 Oak St New York, NY, 10001</v>
+      </c>
+      <c r="L21" t="str" cm="1">
+        <f t="array" ref="L21:M21">_xlfn.TEXTSPLIT(B21, " ",)</f>
+        <v>Jim</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="O21" t="str">
+        <f t="shared" si="1"/>
+        <v>567</v>
+      </c>
       <c r="Q21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="R21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
+        <v>NY</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="V21" t="str">
+        <f t="shared" si="7"/>
         <v>NY</v>
       </c>
     </row>
@@ -2629,21 +3172,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BCB134-41DE-47D5-9456-1C60C9867AFA}">
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="3" width="27.265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.59765625" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="29.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -2672,7 +3215,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
@@ -2702,7 +3245,7 @@
         <v>457 Oak St San Jose, CA, 95101</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>71</v>
       </c>
@@ -2732,7 +3275,7 @@
         <v>203 Birch St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -2762,7 +3305,7 @@
         <v>790 Pine St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -2792,7 +3335,7 @@
         <v>457 Oak St San Jose, CA, 95101</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -2822,7 +3365,7 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -2852,7 +3395,7 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -2882,7 +3425,7 @@
         <v>790 Pine St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
@@ -2912,7 +3455,7 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -2942,7 +3485,7 @@
         <v>123 Elm St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>80</v>
       </c>
@@ -2972,7 +3515,7 @@
         <v>123 Elm St Los Angeles, CA, 90001</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -3002,7 +3545,7 @@
         <v>123 Elm St San Diego, CA, 92101</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>82</v>
       </c>
@@ -3032,7 +3575,7 @@
         <v>202 Birch St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
@@ -3062,7 +3605,7 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -3092,7 +3635,7 @@
         <v>123 Elm St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
@@ -3122,7 +3665,7 @@
         <v>456 Oak St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -3152,7 +3695,7 @@
         <v>203 Birch St Chicago, IL, 60602</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -3182,7 +3725,7 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -3212,7 +3755,7 @@
         <v>456 Oak St New York, NY, 10001</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -3242,7 +3785,7 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -3280,23 +3823,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F197DD-EE87-4022-A4E6-1027B6E64DD6}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29" style="9" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="11.86328125" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -3338,7 +3881,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
@@ -3383,7 +3926,7 @@
         <v>0123548</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>71</v>
       </c>
@@ -3427,7 +3970,7 @@
         <v>0123549</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -3471,7 +4014,7 @@
         <v>0123550</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -3515,7 +4058,7 @@
         <v>0123551</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -3559,7 +4102,7 @@
         <v>0123552</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -3600,7 +4143,7 @@
         <v>0123553</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -3641,7 +4184,7 @@
         <v>0123554</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
@@ -3682,7 +4225,7 @@
         <v>0123555</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -3723,7 +4266,7 @@
         <v>0123556</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>80</v>
       </c>
@@ -3764,7 +4307,7 @@
         <v>0123557</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -3805,7 +4348,7 @@
         <v>0123558</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>82</v>
       </c>
@@ -3846,7 +4389,7 @@
         <v>0123559</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
@@ -3887,7 +4430,7 @@
         <v>0123560</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -3928,7 +4471,7 @@
         <v>0123561</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
@@ -3969,7 +4512,7 @@
         <v>0123562</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -4010,7 +4553,7 @@
         <v>0123563</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -4051,7 +4594,7 @@
         <v>0123564</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -4092,7 +4635,7 @@
         <v>0123565</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -4133,7 +4676,7 @@
         <v>0123566</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -4182,21 +4725,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E73CB36-69AF-4B27-BCC8-FDB353A4DE72}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.1328125" customWidth="1"/>
-    <col min="5" max="5" width="26.1328125" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" customWidth="1"/>
     <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="40" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.59765625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="9.1328125" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -4227,7 +4770,7 @@
       <c r="K1" s="17"/>
       <c r="L1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
@@ -4265,7 +4808,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>71</v>
       </c>
@@ -4303,7 +4846,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -4341,7 +4884,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -4379,7 +4922,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -4417,7 +4960,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -4455,7 +4998,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -4493,7 +5036,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
@@ -4531,7 +5074,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -4569,7 +5112,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>80</v>
       </c>
@@ -4607,7 +5150,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -4645,7 +5188,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>82</v>
       </c>
@@ -4683,7 +5226,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
@@ -4721,7 +5264,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -4759,7 +5302,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
@@ -4797,7 +5340,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -4835,7 +5378,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -4873,7 +5416,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -4911,7 +5454,7 @@
         <v>NY</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -4949,7 +5492,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -4998,30 +5541,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85789AE4-586B-4DA1-B069-1172780CDADC}">
   <dimension ref="A2:BW25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.3984375" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>94</v>
       </c>
       <c r="B2" s="16"/>
     </row>
-    <row r="3" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>_xlfn.TEXTJOIN(", ",TRUE,Data!H2:H21)</f>
         <v>Kafka, DataBricks, Spark, Python, GCP, Power BI, GCP, Airflow, Hadoop, R, Azure, Java, SQL, DataBricks, Kafka, DataBricks, Spark, Python, GCP, DataBricks, Hadoop, Java, Snowflake, Airflow, DataBricks, Azure, Java, SQL, DataBricks, Snowflake, Airflow, DataBricks, Scala, Azure, R, Kafka, Snowflake, Excel, Scala, Excel, Power BI, R, Scala, R, Hadoop, Power BI, SQL, Snowflake, Airflow, DataBricks, Java, Scala, R, DataBricks, Azure, Scala, Power BI, GCP, Airflow, Hadoop, R, DataBricks, Hadoop, Java, Snowflake, Power BI, Tableau, Airflow, SQL, DataBricks, Hadoop, Java, DataBricks, Hadoop, Java</v>
       </c>
     </row>
-    <row r="5" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>67</v>
       </c>
       <c r="B5" s="16"/>
     </row>
-    <row r="6" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A6" t="str" cm="1">
         <f t="array" ref="A6:BW6">_xlfn.TEXTSPLIT(A3,", ")</f>
         <v>Kafka</v>
@@ -5249,7 +5792,7 @@
         <v>Java</v>
       </c>
     </row>
-    <row r="8" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>68</v>
       </c>
@@ -5261,157 +5804,157 @@
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
     </row>
-    <row r="9" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str" cm="1">
-        <f t="array" ref="A9:A25">_xlfn.UNIQUE(TRANSPOSE(6:6))</f>
-        <v>Kafka</v>
+        <f t="array" ref="A9:A25">_xlfn._xlws.SORT(_xlfn.UNIQUE(TRANSPOSE(6:6)),1,-1)</f>
+        <v>Tableau</v>
       </c>
       <c r="B9" s="1">
         <f>COUNTIF($6:$6,A9)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:75" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
-        <v>DataBricks</v>
+        <v>SQL</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" ref="B10:B25" si="0">COUNTIF($6:$6,A10)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:75" x14ac:dyDescent="0.45">
+        <f>COUNTIF($6:$6,A10)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <v>Spark</v>
       </c>
       <c r="B11" s="1">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($6:$6,A11)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
+        <v>Snowflake</v>
+      </c>
+      <c r="B12" s="1">
+        <f>COUNTIF($6:$6,A12)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="str">
+        <v>Scala</v>
+      </c>
+      <c r="B13" s="1">
+        <f>COUNTIF($6:$6,A13)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="str">
+        <v>R</v>
+      </c>
+      <c r="B14" s="1">
+        <f>COUNTIF($6:$6,A14)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="str">
         <v>Python</v>
       </c>
-      <c r="B12" s="1">
-        <f t="shared" si="0"/>
+      <c r="B15" s="1">
+        <f>COUNTIF($6:$6,A15)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:75" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="str">
+    <row r="16" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="B16" s="1">
+        <f>COUNTIF($6:$6,A16)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="str">
+        <v>Kafka</v>
+      </c>
+      <c r="B17" s="1">
+        <f>COUNTIF($6:$6,A17)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="str">
+        <v>Java</v>
+      </c>
+      <c r="B18" s="1">
+        <f>COUNTIF($6:$6,A18)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="str">
+        <v>Hadoop</v>
+      </c>
+      <c r="B19" s="1">
+        <f>COUNTIF($6:$6,A19)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="str">
         <v>GCP</v>
       </c>
-      <c r="B13" s="1">
-        <f t="shared" si="0"/>
+      <c r="B20" s="1">
+        <f>COUNTIF($6:$6,A20)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:75" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="str">
-        <v>Power BI</v>
-      </c>
-      <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:75" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="str">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="str">
+        <v>Excel</v>
+      </c>
+      <c r="B21" s="1">
+        <f>COUNTIF($6:$6,A21)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="str">
+        <v>DataBricks</v>
+      </c>
+      <c r="B22" s="1">
+        <f>COUNTIF($6:$6,A22)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="str">
+        <v>Azure</v>
+      </c>
+      <c r="B23" s="1">
+        <f>COUNTIF($6:$6,A23)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="str">
         <v>Airflow</v>
       </c>
-      <c r="B15" s="1">
-        <f t="shared" si="0"/>
+      <c r="B24" s="1">
+        <f>COUNTIF($6:$6,A24)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:75" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="str">
-        <v>Hadoop</v>
-      </c>
-      <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="1" t="str">
-        <v>R</v>
-      </c>
-      <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" s="1" t="str">
-        <v>Azure</v>
-      </c>
-      <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" s="1" t="str">
-        <v>Java</v>
-      </c>
-      <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" s="1" t="str">
-        <v>SQL</v>
-      </c>
-      <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" s="1" t="str">
-        <v>Snowflake</v>
-      </c>
-      <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" s="1" t="str">
-        <v>Scala</v>
-      </c>
-      <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" s="1" t="str">
-        <v>Excel</v>
-      </c>
-      <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" s="1" t="str">
-        <v>Tableau</v>
-      </c>
-      <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>0</v>
       </c>
       <c r="B25" s="1">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($6:$6,A25)</f>
         <v>0</v>
       </c>
     </row>
